--- a/affiliate_data/เครื่องใช้ในบ้าน.xlsx
+++ b/affiliate_data/เครื่องใช้ในบ้าน.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Shopee Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shopee Products" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4500,6 +4500,806 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ทีวี 32 นิ้ว ทีวี 43 นิ้ว Smart TV 4K LED โทรทัศน์ ทีวีจอแบน สมาร์ททีวี ระบบ Android ทีวีดิจิตอล รับประกัน 1ปี</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mp3uikhs59n0d1.webp</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3689.00</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ขายได้ 30พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/16016084045</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2VrqMwDZNm</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>New เสื้อฮู้ด Stussy Hoodie แท้100% สําหรับผู้ชาย และผู้หญิง หลวมเสื้อฮู้ด</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mln7lyct3shvb7.webp</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1680.00</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ขายได้ 488 ชิ้น</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/25531971678</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B7XABAYi0</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Lifinity ชั้นวางจาน ที่คว่ำจาน 120/105ซม ชั้นวางของในครัว</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m6m8v000vb5b5e.webp</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>678.00</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>ขายได้ 6พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/8442385823</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qc9ZkOEib</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>XTREM เคส iPhone 18/17/16/15/14 เปลี่ยนรูปได้ เคสเปลี่ยนรูป เคสไอโฟน เคสมือถือ Magnetic Screen Case NFC จอ E-Ink</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-8259f-mt18gjog1xj6a4.webp</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2250.00</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ขายได้ 2พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/55250250242</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6q0pWwhhQ9</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Pacsafe CX Anti-Theft Square Crossbody กระเป๋ากันขโมย กระเป๋าสะพายข้าง สำหรับเดินทางและใช้งานทุกวัน | Fits 8" Tablet</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-msmmfx079j4163.webp</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>4100.00</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>ขายได้ 410 ชิ้น</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/19781507501</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VzJBAKIWf</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BOYA mini 2 ไมค์ไร้สาย ตัดเสียงรบกวน AI ไมค์อัดเสียง สําหรับ Type-C iPhone/Android ไมค์ไลฟ์สด</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-miwe8y7c5edg26.webp</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>1319.00</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ขายได้ 8พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/28167956378</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AOkJG7XeU</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>[HOT]AXON Mega Smart Watch จอใหญ่AMOLED 1.85",แบตอึด,โทรได้,วัดชีพจร SpO2 ,วัดการนอน,โหมดออกกำลังกาย100+, IP68 ประกัน2ปี</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mpj9ta3nkqvj7a.webp</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>1798.00</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ขายได้ 10พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/25527756989</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1AVOUsEit</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Pacsafe GO Anti-Theft Saddle Crossbody กระเป๋ากันขโมย กระเป๋าสะพายข้าง สำหรับเดินทางและใช้งานทุกวัน</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-msmlbhosfs3o57.webp</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>4730.00</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>ขายได้ 915 ชิ้น</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/24406480605</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4Vcukm6B7Q</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>[ซื้อ 1 แถม 6] 2026 แท็บเล็ตพีซี 12.0 นิ้ว 12000mAh แบตเตอรี่ 4G / 5G แท็บเล็ต Dual SIM Android 12.0 แท็บเล็ต COD</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mhlffavqeo7c65.webp</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>1799.00</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>ขายได้ 2พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/15397566471</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60RiXXMOj0</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ANCHI จักรยานพับได้ จักรยานแม่บ้าน จักรยาน แม่บ้าน ญี่ปุ่น เกียร์ 7 ระดับ ตะกร้าเหล็ก จักรยานผู้ใหญ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mlw25x1168zm9d.webp</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1955.00</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ขายได้ 6พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/45704393767</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4B04MAcB1P</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Hisense TV 55 นิ้ว รุ่น 55E6Q 4K Ultra HD Smart TV Voice Control WIFI Build in Netflix</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mt5hov1ntfr612.webp</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>9490.00</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ขายได้ 10พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/18478170373</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/50ZBLhh7GG</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>เครื่องตัดกิ่งไม้ไร้สาย ตัดแต่งพุ่มไม้ แต่งกิ่งไม้ เครื่องตัดหญ้าไฟฟ้า เลื่อยตัดแต่งสวน ตัดแต่งพุ่มหญ้า</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul9-ljuyqy4onhnq0b.webp</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>875.00</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>ขายได้ 3พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/22549935932</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9KiAVfeVSA</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>【รับประกัน 5ปี】elago เครื่องตัดหญ้าไฟฟ้าไร้สาย แบบพกพา ปรับได้ ยืดหด 5000mAh*2 อุปกรณ์ครบชุด พร้อมแบตเตอรีลิเธียมแท้</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mq1py5gj48ox05.webp</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>634.00</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>ขายได้ 6พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/42006405121</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5VVRwdnTF3</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>XTREM เคส iPhone 17 เปลี่ยนรูปได้ เคสเปลี่ยนรูป เคสมือถือ เคสไอโฟน Magnetic Screen Case NFC หน้าจอ E-Ink</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-msy2myjf83rbdd.webp</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2750.00</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ขายได้ 566 ชิ้น</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/49303516193</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fZwWdSAZ8</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>[Best Seller] TCL แอร์ Full DC SaveIn AI Inverter ประหยัดไฟ ขนาด 9,200- 24,200 BTU รุ่น TAC-XALCH2</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-msjawf9q8e808c.webp</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>14290.00</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>ขายได้ 100พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/13181175093</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zxrIvShk4</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>เคส iPhone 18 Pro Max 18 Pro 17 Air 16 Series Ultra Hybrid T MagFit Spigen - รองรับ Camera Control</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134207-825am-msxh4293k0sp86.webp</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>1287.00</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>ขายได้ 15 ชิ้น</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/52809274489</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4VcukpE2bD</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>KEEN รองเท้าแตะรัดส้น ชายหญิง กันกระแทกส้นและนิ้วเท้า กันลื่นยางแท้ทุกพื้น เป่าไว ซับนิ่ม เดินป่าทางชัน</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-moggu9b4ekn405.webp</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2429.00</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>ขายได้ 37 ชิ้น</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/54710832898</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2LYQAr4Hov</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2024 สไตล ์ ใหม ่ Star alpinestars a รถจักรยานยนต ์ Warm Shock-resistant Cycling Jersey Casual แจ ็ คเก ็ ตผู ้ ชายผู ้ หญิงฤดูใบไม ้ ผลิฤดูใบไม ้ ร ่ วงฤดูหนาว Soft Shell แจ ็ คเก ็ ตกันน ้ ํา Star แจ ็ คเก ็ ตสองสี</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7r98o-luf6vg0dv0xw51.webp</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2107.00</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>ขายได้ 128 ชิ้น</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/25275966912</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3VkNZ0QFA2</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
